--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0055.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0055.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Left Hook</t>
+          <t>Móc trái</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Bạn cảm thấy bình yên trong lòng</t>
+          <t>Ngươi cảm thấy lòng mình bình yên lạ thường.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Đến phòng tiếp theo</t>
+          <t>Tiến vào phòng tiếp theo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Qianzhang</t>
+          <t>Kiền Chương</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Quả cầu Điều khiển của Tòa án Savantae</t>
+          <t>Quả Cầu Điều Khiển của Court of Savantae</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Fluffy Gryphon</t>
+          <t>Sư tử đầu đại bàng lông bông</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Hydro Orb</t>
+          <t>Quả Cầu Thủy</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Tội lỗi của Bầy đàn: Voila</t>
+          <t>Tội Ác Của Bầy Đàn: Voila</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Khạc khạc...</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Cô gái thơm</t>
+          <t>Cô Gái Thơm Mùi Hương</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Observe</t>
+          <t>Quan Sát</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Inspect Shorekeeper's Illusion</t>
+          <t>Kiểm tra Ảo Ảnh Người Giữ Bờ</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Thành viên Bờ biển Đen</t>
+          <t>Thành Viên Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Đàn xếp</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu Dịu dàng</t>
+          <t>Nhà nghiên cứu dịu dàng</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Dịch chuyển đến đáy Trạm Không gian</t>
+          <t>Dịch chuyển xuống đáy Trạm Không Gian</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Shorekeeper Cube</t>
+          <t>Khối Shorekeeper</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Ký ức về Trận đấu Sinh tử</t>
+          <t>Ký Ức Đọ Sức</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Đi dọn dẹp</t>
+          <t>Đi dọn dẹp đi.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Phantom - Lightcrusher</t>
+          <t>Ảo Ảnh - Nghiền Ánh</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Nhận Guide Crystal</t>
+          <t>Nhận Đá Hướng Dẫn</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Eastern Forest Cage</t>
+          <t>Lồng giam Rừng Đông</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Trưởng lão Im lặng</t>
+          <t>Trưởng Lão Vô Tiếng</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Lana</t>
+          <t>Lana.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Confinement Trap</t>
+          <t>Bẫy Giam Cầm</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Autopuppet Scout</t>
+          <t>Trinh Sát Tự Động</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Thương nhân Háo hức</t>
+          <t>Thương Nhân Hăng Hái</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Examine</t>
+          <t>Kiểm Tra</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Vào Somnoire</t>
+          <t>Bước vào Somnoire</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Cluster Prism: Glacio</t>
+          <t>Lăng Kính Cụm: Glacio</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Abyss Luminary</t>
+          <t>Huyễn Tinh Vực Sâu</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Tacetite Cage</t>
+          <t>Lồng Tacetite</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Tắt thiết bị liên lạc</t>
+          <t>Tắt thiết bị liên lạc đi</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Ta</t>
+          <t>Tao</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Voidworm</t>
+          <t>Giun Voidworm</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Synthesize</t>
+          <t>Tổng hợp</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Thử thách lại</t>
+          <t>Thử Thách Lại</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Granpa Gan</t>
+          <t>Ông nội Gan</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Audio Log 2</t>
+          <t>Nhật Ký Âm Thanh 2</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Đội trưởng Đội Hiệp hội Tiên phong</t>
+          <t>Đội trưởng Đội Tiên phong</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Rời Viện Nghiên cứu</t>
+          <t>Rời khỏi Viện Nghiên cứu</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Chuyển sang không gian Aurora</t>
+          <t>Chuyển sang không gian Ánh Sáng Cực Quang</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Giai đoạn III</t>
+          <t>Giai Đoạn III</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Changli Cube</t>
+          <t>Khối Changli</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Bắt đầu thử thách</t>
+          <t>Bắt đầu Thử thách</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Excited Junior</t>
+          <t>Cậu nhóc háo hức</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Khách hàng điên loạn</t>
+          <t>Khách Hàng Cuồng Loạn</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Bộ Tạo Lộ Trình</t>
+          <t>Bộ Điều Hướng</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Máy thử nghiệm: Dài ngoài trời</t>
+          <t>Máy Kiểm Tra: Ngoài trời (dài)</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Phantom Kerasaur</t>
+          <t>Ảo Ảnh Kerasaur</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Isth</t>
+          <t>Isth...</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Song</t>
+          <t>Khúc Ca</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Liliania</t>
+          <t>Liliana</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Gemini Spore</t>
+          <t>Bào tử Song Tử</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Have Bạn Seen My Clockatoo</t>
+          <t>Cậu có thấy chú vẹt đồng hồ của tớ đâu không?</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Nhân viên văn phòng mệt mỏi</t>
+          <t>Nhân Viên Văn Phòng Mệt Phờ</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Sandbag</t>
+          <t>Bao Cát</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Hoochief Menace</t>
+          <t>Hăm Dọa Thủ Lĩnh Hoo</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Snow Crane</t>
+          <t>Hạc Tuyết</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Mining Reindeer</t>
+          <t>Tuần Lộc Khai Thác</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Upper Layer Seq Playback Controller</t>
+          <t>Bộ Điều Khiển Phát Lại Trình Tự Tầng Thượng</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Collapsed Entrance</t>
+          <t>Lối Vào Sụp Đổ</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Vào Rabelle College</t>
+          <t>Vào Học viện Rabelle</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Qiuwang</t>
+          <t>Thu Vương</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Thanh tra Fractsidus</t>
+          <t>Thanh Tra Fractsidus</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Ngồi bên cô ấy</t>
+          <t>Ngồi bên cô ấy đi</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Retired Fisherman</t>
+          <t>Ngư Phủ Hưu Trí</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Bảng thông báo: tạm thời</t>
+          <t>Bảng tin: Tạm thời</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Nhận Corroder</t>
+          <t>Nhận được Corroder</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Cubieverse</t>
+          <t>Vũ Trụ Cubie</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Xinle</t>
+          <t>Tân Lạc</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Ragged Tent</t>
+          <t>Lều Rách Nát</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Guarding Acolyte</t>
+          <t>Tín Đồ Canh Gác</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Aunt Qiu</t>
+          <t>Dì Qiu</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Cư dân tập trung</t>
+          <t>Tập trung "Cư Dân"</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Stone Lift</t>
+          <t>Nâng Đá</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Xiaotang</t>
+          <t>Tiểu Đường</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Đến tầng thấp</t>
+          <t>Tầng mặt đất</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Deliver Materials</t>
+          <t>Giao Vật Liệu</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Nhân viên bình tĩnh</t>
+          <t>Nhân Viên Điềm Tĩnh</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Strange Telephone Booth</t>
+          <t>Buồng điện thoại kỳ lạ</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Zealous Pioneer Association Phóng viên</t>
+          <t>Phóng Viên Hiệp Hội Người Tiên Phong Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Pin</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Witch's Illusion</t>
+          <t>Ảo Ảnh Phù Thủy</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Forgotten Order</t>
+          <t>Hội Bị Lãng Quên</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Exam Zone 2</t>
+          <t>Khu Vực Thi 2</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Loud Gladiator</t>
+          <t>Dũng Sĩ Hùng Hồn</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Edodes</t>
+          <t>Nấm hương</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Fowl</t>
+          <t>Gia Cầm</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Shadow of Fisalia</t>
+          <t>: Shadow of Fisalia</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Skavitz's Staff</t>
+          <t>Gậy của Skavitz</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Leonidas Hotel</t>
+          <t>Khách sạn Leonidas</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Gladiator's Portrait</t>
+          <t>Chân Dung Đấu Sĩ</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Người đàn ông bí ẩn</t>
+          <t>Người Đàn Ông Bí Ẩn</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>: Dream Remnants</t>
+          <t>: Tàn Tích Giấc Mơ</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Lava Larva</t>
+          <t>Ấu trùng dung nham</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>The False Sovereign: Dark Serpent</t>
+          <t>Hư Vương: Rắn Hắc Ám</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Vào Heart of the Crownless</t>
+          <t>Đến với Trái Tim Vô Vương</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Peddley Prototype</t>
+          <t>Mẫu Thử Peddley</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Neon Tower: Mê Cung Vòng Lặp (Khởi động lại)</t>
+          <t>Tháp Neon: Mê Cung Vòng Lặp (Khởi Động Lại)</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Light Converger</t>
+          <t>Người Hội Tụ Ánh Sáng</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Endless Battle</t>
+          <t>Trận Chiến Vô Tận</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Observe</t>
+          <t>Quan Sát</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Titanhorn Antelope</t>
+          <t>Linh Dương Sừng Titan</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Whiff Whaff: Wind</t>
+          <t>Phì Phò: Gió</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Lenie</t>
+          <t>Lenie...</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Nhà Thám Hiểm Vô Danh - Tù Nhân Bị Bỏ Rơi Trong Bóng Tối</t>
+          <t>Nhà Thám Hiểm Vô Danh - Tù Nhân Bị Đẩy Xuống Bóng Tối</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Wishing Stall</t>
+          <t>Gian Hàng Ước Nguyện</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Deflection Board</t>
+          <t>Bảng Né Tránh</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Think</t>
+          <t>Suy nghĩ đi</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Flamecrest Gladiator</t>
+          <t>Dũng Sĩ Flamecrest</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Impassioned Youth</t>
+          <t>Thanh Niên Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Tôi muốn giao Sonance Caskets: Ragunna</t>
+          <t>Tao muốn giao Cỗ Quan Sonance: Ragunna</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Một bia mộ ẩn trong giấc mơ</t>
+          <t>Ngôi mộ chìm trong màn sương mộng</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Kronaclaw</t>
+          <t>Móng Vuốt Hắc Ám</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Exoswarm Enthusiast</t>
+          <t>Người Hâm Mộ Exoswarm</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Doudou</t>
+          <t>Đậu Đậu</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Tanning</t>
+          <t>Làm rám nắng</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Havoc Warrior</t>
+          <t>Chiến Binh Hỗn Loạn</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Thành viên nhóm không hài lòng</t>
+          <t>Thành viên đội không hài lòng</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Uncle Bin</t>
+          <t>Chú Tân</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Namipon Lightbox</t>
+          <t>Đèn hộp Namipon</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Dark: Hoartoise</t>
+          <t>Hắc: Hoartoise</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Yinfeng</t>
+          <t>Âm Phong</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Magnus's Mother</t>
+          <t>Mẹ của Magnus</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Arithmetic Shell</t>
+          <t>Vỏ Giáp Số Học</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Vào</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Long'er</t>
+          <t>Lâu lắm...</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Cổng Không Gian</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Vault Ground Floor Entry</t>
+          <t>Lối Vào Tầng Trệt Kho Tàng</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Shixia</t>
+          <t>Thạch Hạ</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Mia…</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Grandma Hua</t>
+          <t>Bà Hua</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Devotee's Flesh</t>
+          <t>Thịt Tín Đồ</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Phantom- Lightcrusher</t>
+          <t>Bóng Ma - Nghiền Ánh Sáng</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Thành viên gia đình Montelli nghiêm túc</t>
+          <t>Thành Viên Gia Tộc Montelli Đứng Đắn</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>"Supply Receipt Register Template"</t>
+          <t>"Mẫu Sổ Đăng Ký Biên Lai Cung Ứng"</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Phoenix Butterfly</t>
+          <t>Bướm Phượng Hoàng</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Du ký Ký ức</t>
+          <t>Biên Niên Ký Ức</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Photon Lock</t>
+          <t>Khóa Photon</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Vào</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu hào hứng</t>
+          <t>Nhà nghiên cứu hứng thú</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Yangming</t>
+          <t>Dương Minh</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Thắp đèn và tìm cô ấy</t>
+          <t>Thắp sáng ngọn đèn và tìm nàng</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Đạt Cấp 1 Data Hub để mở khóa</t>
+          <t>Đạt Cấp Trung Tâm Dữ Liệu 1 để mở khóa.</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>- Móng Vuốt Của Sự Điên Loạn</t>
+          <t>- Vuốt Hoang Tưởng</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Người đàn ông bình thường</t>
+          <t>Người Đàn Ông Thư Thái</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Pin sắp hết pin</t>
+          <t>Pin của cậu sắp hết rồi</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Xuxu</t>
+          <t>Tú Tú</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Trao đổi</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Dusk Honeypot</t>
+          <t>Bình Minh Của Chiếc Lọ Mật</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Disruptor Noise</t>
+          <t>Âm Thanh Disruptor</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Anh ấy Chang</t>
+          <t>Hà Xương</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Suspicious TARD-E</t>
+          <t>TARD-E Đáng Ngờ</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Vào ký túc xá Học viện</t>
+          <t>Vào ký túc xá của Học Viện</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>KU-Clinic</t>
+          <t>Phòng Khám KU</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Tấn công ngược</t>
+          <t>Tấn Công ngược chiều</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Final Pillar</t>
+          <t>Trụ Cột Cuối Cùng</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Trilan</t>
+          <t>Tam quẻ</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>"Paradoxical Karma"</t>
+          <t>Nghiệp nghịch lý</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Rusty Kiếm</t>
+          <t>Kiếm Gỉ</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Arrogant Duelist</t>
+          <t>Kẻ Khiêu Chiến Kiêu Ngạo</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Duel Again</t>
+          <t>Đấu lại</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Name Explorer Grapple</t>
+          <t>Đấu Trường Đặt Tên</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Oil Painting</t>
+          <t>Bức Tranh Dầu</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Client Activator</t>
+          <t>Bộ kích hoạt Khách hàng</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Young Dreadmane: Fire</t>
+          <t>Dreadmane Trẻ: Lửa</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Lo Lắng</t>
+          <t>Nhà Nghiên Cứu Lo Âu</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Dungeon_Air Wall Manager_Box</t>
+          <t>Quản lý Rào Cản Không Gian_Tủ</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Call Initiator</t>
+          <t>Gọi Người Khởi Xướng</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Nervous Exile</t>
+          <t>Kẻ Lưu Đày Lo Lắng</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Glowing Frostbite Tertoise</t>
+          <t>Rùa Sương Giá Phát Quang</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Sit</t>
+          <t>Ngồi đi</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Nhân Viên Hỗ Trợ Nghiêm Túc</t>
+          <t>Nhân viên Hậu cần Nghiêm túc</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Tang Manliu</t>
+          <t>Đường Manliu</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Smartprint Cube</t>
+          <t>Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Brother Jie</t>
+          <t>Anh Kiệt</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Adventurer Namipon</t>
+          <t>Nhóc Phiêu Lưu Namipon</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Noisy Kids</t>
+          <t>Bọn Trẻ Huyên Náo</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Điều tra tần số</t>
+          <t>Kiểm tra tần số</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Pollutants</t>
+          <t>Chất ô nhiễm</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Bo Yu</t>
+          <t>Bạch Ngọc</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Khu Vực Thử Thách V</t>
+          <t>Khu vực thử thách V</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Kiểm tra bức tranh</t>
+          <t>Xem bức tranh kia</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Đưa ra lời hướng dẫn</t>
+          <t>Đưa ra lời chỉ dẫn</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Request Gondola</t>
+          <t>Yêu Cầu Gondola</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Dịch chuyển đến lối ra</t>
+          <t>Dịch chuyển ra lối thoát</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Namipon Courier</t>
+          <t>Namipon Đặc Nhiệm</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Cậu Bé Nhỏ</t>
+          <t>Cậu Bé</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Uncle Dong</t>
+          <t>Chú Đông</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Beam Weapon Firing Mechanism</t>
+          <t>Cơ Chế Phóng Tia</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Augusta có thể phá hủy 1</t>
+          <t>Augusta có thể bị phá hủy 1</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Luminous Calendula</t>
+          <t>Cúc Vàng Rực Rỡ</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Matrix Mimic: Illusory Treasure</t>
+          <t>Bắt Chước Ma Trận: Bảo Vật Ảo</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Brutal Bear</t>
+          <t>Gấu Hung Tàn</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Diamondclaw: Venom</t>
+          <t>Diamondclaw: Nọc Độc</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Nhìn quanh căn cứ</t>
+          <t>Khám phá căn cứ</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Iris</t>
+          <t>Hoa Diên Vĩ</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Register Personal Info</t>
+          <t>Đăng ký thông tin cá nhân</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Xiaosui</t>
+          <t>Tiểu Tuệ</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Đi tưới hoa ở phía bên kia</t>
+          <t>Đi tưới hoa ở bên kia nữa</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Excited Wootter</t>
+          <t>Người dùng Wootter hưng phấn</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Đọc tập tin</t>
+          <t>Đọc tập tài liệu</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Cư dân lo lắng</t>
+          <t>Cư Dân Lo Sợ</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Inspect</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Tập audio - Hòm Sonance Làng Thú Nhồi Bông</t>
+          <t>Vở Kịch Âm Thanh - Hòm Sonance Làng Thú Nhồi Bông</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Climbing Fig</t>
+          <t>Cây Sung Leo</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Cà phê</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>KU-Scout</t>
+          <t>KU-Tình Báo</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Thoát khỏi Vòng lặp Thời gian</t>
+          <t>Rời khỏi Vòng lặp Thời gian đi</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Sunflare Everlasting</t>
+          <t>Vĩnh Hằng Ánh Dương</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Thoughtful Actor</t>
+          <t>Diễn viên Chu Đáo</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Shunlian</t>
+          <t>Thuận Liên</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu giải thích</t>
+          <t>Nhà Nghiên Cứu Đang Giải Thích</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Konglin</t>
+          <t>Khổng Lâm</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Tacet Discord: Crownless: Hạ gục bản sao trong một đòn</t>
+          <t>Tacet Discord: Crownless: Clone one hit kill</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Chongshan</t>
+          <t>Sùng Sơn</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Liuxian</t>
+          <t>Lục Hiền</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Wind Trail</t>
+          <t>Dấu Vết Gió</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Gladiator của Hadrian</t>
+          <t>Đấu sĩ của Hadrian</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Sigrika's Diary</t>
+          <t>Nhật ký của Sigrika</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Đạt Cấp 4 Trung Tâm Dữ Liệu để mở khóa</t>
+          <t>Đạt Cấp Trung Tâm Dữ Liệu 4 để mở khóa.</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Kích hoạt Beam Weapon</t>
+          <t>Kích hoạt Vũ Khí Tia Chùm</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Moon Shooter</t>
+          <t>Bắn Trăng</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Gợi ý một bộ phim tình cảm</t>
+          <t>Gợi ý một bộ phim tình cảm đi</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>: Stormborn Menace</t>
+          <t>: Mối Đe Dọa Bão Tố</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Interact</t>
+          <t>Tương Tác</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Gọi thang máy</t>
+          <t>Gọi Thang Máy</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Yuancai</t>
+          <t>Nguyên Thái</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>New Recruit</t>
+          <t>Tân Binh Mới</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>The K626 Resolution</t>
+          <t>Nghị quyết K626</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Mystery Dreamland</t>
+          <t>Mộng Ảo Kỳ Bí</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Ocean Moonfish</t>
+          <t>Cá Trăng Đại Dương</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Giải câu đố</t>
+          <t>Giải câu đố đi</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Enter Simulation Training</t>
+          <t>Vào Huấn luyện Mô phỏng</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Illumination Device</t>
+          <t>Thiết Bị Chiếu Sáng</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Unusual Figures</t>
+          <t>Những Hình Dáng Kỳ Lạ</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Baths Seats</t>
+          <t>Ghế Nhà Tắm</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Đặt lại Patterns</t>
+          <t>Đặt lại Mẫu Hình</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Lối vào Dark Side</t>
+          <t>Lối vào Mặt Tối</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
